--- a/Aji_game copy_Feb.xlsx
+++ b/Aji_game copy_Feb.xlsx
@@ -1583,11 +1583,17 @@
           <c:cat>
             <c:numRef>
               <c:f>'User Engagement'!$A$36:$A$94</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy</c:formatCode>
+              </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'User Engagement'!$B$36:$B$94</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1630,11 +1636,17 @@
           <c:cat>
             <c:numRef>
               <c:f>'User Engagement'!$A$36:$A$94</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy</c:formatCode>
+              </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'User Engagement'!$C$36:$C$94</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1991,12 +2003,18 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'gameplay_report(score) '!$A$67:$A$94</c:f>
+              <c:f>'gameplay_report(score) '!$A$36:$A$94</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy</c:formatCode>
+              </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'gameplay_report(score) '!$B$67:$B$94</c:f>
+              <c:f>'gameplay_report(score) '!$B$36:$B$94</c:f>
+              <c:numCache>
+                <c:formatCode>0,"k"</c:formatCode>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -2289,11 +2307,17 @@
           <c:cat>
             <c:numRef>
               <c:f>'gameplay_report(time) '!$A$36:$A$94</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy</c:formatCode>
+              </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'gameplay_report(time) '!$B$36:$B$94</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -2634,6 +2658,9 @@
           <c:val>
             <c:numRef>
               <c:f>state!$B$12:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -2977,6 +3004,9 @@
           <c:val>
             <c:numRef>
               <c:f>menu!$B$2:$B$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -3565,6 +3595,9 @@
           <c:val>
             <c:numRef>
               <c:f>score!$C$2:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -13854,457 +13887,582 @@
   <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>recipe_menu</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>total_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ข้าวผัดหมู</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>หมูผัดผงกะหรี่</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ทูน่าลุยสวน</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ไข่พะโล้</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>สุกี้น้ำไก่</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ข้าวหน้าไข่นุ่ม</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>เส้นหมี่ผัดซีอิ๊ว</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ผัดกะเพราเต้าหู้</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>แกงเขียวหวานไก่</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ยำยำแซลมอนขี้เมา</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>รามยอนต้มยำกุ้ง หมูเด้ง</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ข้าวผัดปลาทูน่าหลากสี</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>สลัดอกไก่พริกไทยดำ</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ต้มยำกุ้งรวมเห็ด</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ไข่ม้วนโฮมเมด</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>46</v>
       </c>
-      <c r="B1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2">
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>กะเพราหมูอีซี่</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ทาร์ตไข่โชยุคาราเมล</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>สลัดเต้าหู้ย่างเทริยากิ</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>สลัดแซลมอน</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ผัดผักบุ้งไฟแดง</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>แรปไข่เด็กหอไม่ง้อใคร</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ต้มข่าไก่</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>หมูย่างกับข้าวผัดโหระพา</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ข้าวปั้นพาวเวอร์บอลกะเพรา</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>สปาเก็ตตี้ผัดขี้เมา</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>คิมบับไข่เจียวโต้รุ่ง</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ตับกระเทียม</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ผัดผักรวม</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>เกี๊ยวซ่าซอสเมนไทโกะ</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>แกงจืดมะระยัดไส้หมูสับ</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ยำปลาทูมะเขือสองสี</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ไส้กรอกผัดซอสเทริยากิ</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ไข่ระเบิด</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>โอโคโนมิยากิ สไตล์ฮิโรชิมา</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>เส้นหมี่ไก่ฉีกหมูกระจกรสลาบ</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>โจ๊กหมู</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ไข่เจียวสตีฟโรเจอร์</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>เกี๊ยวซ่าหมูกับต้มเส้นก๋วยจั๊บอุบล</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ผัดไทเพื่อสุขภาพ</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ทอดมันกุ้งห่อไข่</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ยำยำ ต้มยำทะเลหม้อไฟแห้ง</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>สลัดทูน่าแซ่บ</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ก๋วยเตี๊ยวหมูน้ำใส</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>เกี๊ยวซ่าซอสเสฉวน</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>หมูตกครก</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>เบอร์เกอร์หมูควินัว</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>มันฝรั่งอบกับหมูทอด</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>แซนด์วิซเนื้อเทริยากิ</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>พาสต้าผัดหมูหยอง</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ข้าวขยำสมุนไพรกับคอหมูย่าง</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ไข่ตุ๋นจักรพรรดิ์</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ไข่ตุ๋น</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ไข่ดาวน้ำกับสลัดอกไก่โชยุ</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ปีกไก่ทอด</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ก๋วยเตี๋ยวคั่วไก่</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>80</v>
-      </c>
-      <c r="B35">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>82</v>
-      </c>
-      <c r="B36">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>81</v>
-      </c>
-      <c r="B37">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>83</v>
-      </c>
-      <c r="B38">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>84</v>
-      </c>
-      <c r="B39">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>85</v>
-      </c>
-      <c r="B40">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>86</v>
-      </c>
-      <c r="B41">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>87</v>
-      </c>
-      <c r="B42">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>88</v>
-      </c>
-      <c r="B43">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>89</v>
-      </c>
-      <c r="B44">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>90</v>
-      </c>
-      <c r="B45">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B46">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>92</v>
-      </c>
-      <c r="B48">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>94</v>
-      </c>
-      <c r="B49">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>95</v>
-      </c>
-      <c r="B50">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>96</v>
-      </c>
-      <c r="B51">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>97</v>
-      </c>
-      <c r="B52">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>98</v>
-      </c>
-      <c r="B53">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>99</v>
-      </c>
-      <c r="B54">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>100</v>
-      </c>
-      <c r="B55">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>101</v>
-      </c>
-      <c r="B56">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="J59" s="2" t="s">
-        <v>114</v>
+    <row r="57"/>
+    <row r="59" ht="409.6" customHeight="1">
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SELECT 
+    recipe_menu,              
+    COUNT(*) as total_count,
+FROM `dentsu-merkle-ajt.ajt_game_dataset_test.cooking_report`
+WHERE updated_at BETWEEN '2025-11-28 00:00:00' and '2026-02-28 23:59:59'
+GROUP BY 
+    1 -- Group ตาม stage_name (คอลัมน์ที่ 1)
+ORDER BY 
+    2 ASC; </t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -14318,175 +14476,222 @@
   <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>profile_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>line_username</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>total_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tae Tualek</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>534990</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ชมภูนุช995</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>392510</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Oum</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>106370</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>421</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cat chiangmai</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>64170</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CYNN ☃️🥕</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>44290</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>☀️👑Beau542♾🔥🎯</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>17650</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cyberbank</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>15850</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Praewxntkp 🌻🌝</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>11560</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>493</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nim💕</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>11550</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Icezy</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>9800</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>493</v>
-      </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3">
-        <v>11550</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>128</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4">
-        <v>11560</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5">
-        <v>15850</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>125</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6">
-        <v>17650</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>106</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7">
-        <v>44290</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>421</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8">
-        <v>64170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>126</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9">
-        <v>106370</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10">
-        <v>392510</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>62</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11">
-        <v>534990</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" s="13" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" s="13" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="13" t="s">
-        <v>123</v>
+    <row r="12"/>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SELECT </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">profile_id, </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">line_username, </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>SUM(reward_score) AS total_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>FROM `dentsu-merkle-ajt.ajt_game_dataset_test.cooking_report`</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WHERE updated_at &gt;= '2025-11-28 00:00:00' </t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>AND updated_at &lt;= '2026-02-28 23:59:59'</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>GROUP BY profile_id, line_username</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>ORDER BY total_score DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>LIMIT 10;</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Aji_game copy_Feb.xlsx
+++ b/Aji_game copy_Feb.xlsx
@@ -13902,271 +13902,271 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ข้าวผัดหมู</t>
+          <t>ก๋วยเตี๋ยวคั่วไก่</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>238</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>หมูผัดผงกะหรี่</t>
+          <t>ปีกไก่ทอด</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>199</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ทูน่าลุยสวน</t>
+          <t>ไข่ตุ๋น</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>180</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ไข่พะโล้</t>
+          <t>ไข่ดาวน้ำกับสลัดอกไก่โชยุ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>159</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>สุกี้น้ำไก่</t>
+          <t>ข้าวขยำสมุนไพรกับคอหมูย่าง</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ข้าวหน้าไข่นุ่ม</t>
+          <t>ไข่ตุ๋นจักรพรรดิ์</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>เส้นหมี่ผัดซีอิ๊ว</t>
+          <t>พาสต้าผัดหมูหยอง</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ผัดกะเพราเต้าหู้</t>
+          <t>มันฝรั่งอบกับหมูทอด</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>แกงเขียวหวานไก่</t>
+          <t>แซนด์วิซเนื้อเทริยากิ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ยำยำแซลมอนขี้เมา</t>
+          <t>เบอร์เกอร์หมูควินัว</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>รามยอนต้มยำกุ้ง หมูเด้ง</t>
+          <t>หมูตกครก</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ข้าวผัดปลาทูน่าหลากสี</t>
+          <t>ก๋วยเตี๊ยวหมูน้ำใส</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>สลัดอกไก่พริกไทยดำ</t>
+          <t>เกี๊ยวซ่าซอสเสฉวน</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ต้มยำกุ้งรวมเห็ด</t>
+          <t>สลัดทูน่าแซ่บ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ไข่ม้วนโฮมเมด</t>
+          <t>เกี๊ยวซ่าหมูกับต้มเส้นก๋วยจั๊บอุบล</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>กะเพราหมูอีซี่</t>
+          <t>ผัดไทเพื่อสุขภาพ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ทาร์ตไข่โชยุคาราเมล</t>
+          <t>ทอดมันกุ้งห่อไข่</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>สลัดเต้าหู้ย่างเทริยากิ</t>
+          <t>ยำยำ ต้มยำทะเลหม้อไฟแห้ง</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>สลัดแซลมอน</t>
+          <t>ไข่เจียวสตีฟโรเจอร์</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ผัดผักบุ้งไฟแดง</t>
+          <t>โจ๊กหมู</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>แรปไข่เด็กหอไม่ง้อใคร</t>
+          <t>โอโคโนมิยากิ สไตล์ฮิโรชิมา</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ต้มข่าไก่</t>
+          <t>เส้นหมี่ไก่ฉีกหมูกระจกรสลาบ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>หมูย่างกับข้าวผัดโหระพา</t>
+          <t>ไส้กรอกผัดซอสเทริยากิ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ข้าวปั้นพาวเวอร์บอลกะเพรา</t>
+          <t>ไข่ระเบิด</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>สปาเก็ตตี้ผัดขี้เมา</t>
+          <t>ยำปลาทูมะเขือสองสี</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>คิมบับไข่เจียวโต้รุ่ง</t>
+          <t>แกงจืดมะระยัดไส้หมูสับ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ตับกระเทียม</t>
+          <t>เกี๊ยวซ่าซอสเมนไทโกะ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
@@ -14182,271 +14182,271 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>เกี๊ยวซ่าซอสเมนไทโกะ</t>
+          <t>ตับกระเทียม</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>แกงจืดมะระยัดไส้หมูสับ</t>
+          <t>คิมบับไข่เจียวโต้รุ่ง</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ยำปลาทูมะเขือสองสี</t>
+          <t>สปาเก็ตตี้ผัดขี้เมา</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ไส้กรอกผัดซอสเทริยากิ</t>
+          <t>ข้าวปั้นพาวเวอร์บอลกะเพรา</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ไข่ระเบิด</t>
+          <t>หมูย่างกับข้าวผัดโหระพา</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>โอโคโนมิยากิ สไตล์ฮิโรชิมา</t>
+          <t>ต้มข่าไก่</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>เส้นหมี่ไก่ฉีกหมูกระจกรสลาบ</t>
+          <t>แรปไข่เด็กหอไม่ง้อใคร</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>โจ๊กหมู</t>
+          <t>ผัดผักบุ้งไฟแดง</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ไข่เจียวสตีฟโรเจอร์</t>
+          <t>สลัดแซลมอน</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>เกี๊ยวซ่าหมูกับต้มเส้นก๋วยจั๊บอุบล</t>
+          <t>ทาร์ตไข่โชยุคาราเมล</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ผัดไทเพื่อสุขภาพ</t>
+          <t>สลัดเต้าหู้ย่างเทริยากิ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ทอดมันกุ้งห่อไข่</t>
+          <t>ไข่ม้วนโฮมเมด</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ยำยำ ต้มยำทะเลหม้อไฟแห้ง</t>
+          <t>กะเพราหมูอีซี่</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>สลัดทูน่าแซ่บ</t>
+          <t>ต้มยำกุ้งรวมเห็ด</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ก๋วยเตี๊ยวหมูน้ำใส</t>
+          <t>สลัดอกไก่พริกไทยดำ</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>เกี๊ยวซ่าซอสเสฉวน</t>
+          <t>ข้าวผัดปลาทูน่าหลากสี</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>หมูตกครก</t>
+          <t>รามยอนต้มยำกุ้ง หมูเด้ง</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>เบอร์เกอร์หมูควินัว</t>
+          <t>แกงเขียวหวานไก่</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>มันฝรั่งอบกับหมูทอด</t>
+          <t>ยำยำแซลมอนขี้เมา</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>แซนด์วิซเนื้อเทริยากิ</t>
+          <t>ผัดกะเพราเต้าหู้</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>พาสต้าผัดหมูหยอง</t>
+          <t>เส้นหมี่ผัดซีอิ๊ว</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ข้าวขยำสมุนไพรกับคอหมูย่าง</t>
+          <t>ข้าวหน้าไข่นุ่ม</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ไข่ตุ๋นจักรพรรดิ์</t>
+          <t>สุกี้น้ำไก่</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ไข่ตุ๋น</t>
+          <t>ไข่พะโล้</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ไข่ดาวน้ำกับสลัดอกไก่โชยุ</t>
+          <t>ทูน่าลุยสวน</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ปีกไก่ทอด</t>
+          <t>หมูผัดผงกะหรี่</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ก๋วยเตี๋ยวคั่วไก่</t>
+          <t>ข้าวผัดหมู</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57"/>
@@ -14495,132 +14495,132 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Icezy</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>493</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nim💕</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>11550</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Praewxntkp 🌻🌝</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11560</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cyberbank</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15850</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>☀️👑Beau542♾🔥🎯</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>17650</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>106</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CYNN ☃️🥕</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>44290</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>421</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cat chiangmai</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>64170</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Oum</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>106370</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ชมภูนุช995</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>392510</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>62</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Tae Tualek</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C11" t="n">
         <v>534990</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ชมภูนุช995</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>392510</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>126</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Oum</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>106370</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>421</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>cat chiangmai</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>64170</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>106</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CYNN ☃️🥕</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>44290</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>125</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>☀️👑Beau542♾🔥🎯</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>17650</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>cyberbank</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>15850</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>128</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Praewxntkp 🌻🌝</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>11560</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>493</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Nim💕</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>11550</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Icezy</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>9800</v>
       </c>
     </row>
     <row r="12"/>
